--- a/sample_data/wedstrijd-data-2026-09-19.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-19.xlsx
@@ -1183,10 +1183,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>277.885717</v>
+        <v>282.37932</v>
       </c>
       <c r="D7" t="n">
-        <v>234.178171</v>
+        <v>174.201233</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>300.382481</v>
+        <v>316.12939</v>
       </c>
       <c r="D13" t="n">
-        <v>209.883483</v>
+        <v>185.56085</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>300.059779</v>
+        <v>304.740742</v>
       </c>
       <c r="D18" t="n">
-        <v>190.769951</v>
+        <v>179.558663</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>318.131509</v>
+        <v>339.693164</v>
       </c>
       <c r="D19" t="n">
-        <v>222.77112</v>
+        <v>210.594249</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>255.956879</v>
+        <v>246.8091</v>
       </c>
       <c r="D27" t="n">
-        <v>291.559151</v>
+        <v>311.364437</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>231.569864</v>
+        <v>214.293243</v>
       </c>
       <c r="D33" t="n">
-        <v>271.633508</v>
+        <v>281.381671</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>307.267778</v>
+        <v>318.489473</v>
       </c>
       <c r="D36" t="n">
-        <v>288.928456</v>
+        <v>304.844062</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>240.504011</v>
+        <v>206.224442</v>
       </c>
       <c r="D42" t="n">
-        <v>252.818015</v>
+        <v>259.221968</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>313.61113</v>
+        <v>340.183243</v>
       </c>
       <c r="D43" t="n">
-        <v>266.004472</v>
+        <v>280.523583</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-09-19.xlsx
+++ b/sample_data/wedstrijd-data-2026-09-19.xlsx
@@ -1078,10 +1078,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>345.537691</v>
+        <v>388.189034</v>
       </c>
       <c r="D2" t="n">
-        <v>183.765763</v>
+        <v>206.831013</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>107.829018</v>
+        <v>121.138861</v>
       </c>
       <c r="D3" t="n">
-        <v>327.131721</v>
+        <v>368.191464</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>125.942819</v>
+        <v>141.488534</v>
       </c>
       <c r="D4" t="n">
-        <v>335.371605</v>
+        <v>377.465571</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>244.2722</v>
+        <v>274.423866</v>
       </c>
       <c r="D5" t="n">
-        <v>147.674963</v>
+        <v>166.210298</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>130.119574</v>
+        <v>146.180845</v>
       </c>
       <c r="D6" t="n">
-        <v>258.425965</v>
+        <v>290.862145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>282.37932</v>
+        <v>317.234729</v>
       </c>
       <c r="D7" t="n">
-        <v>174.201233</v>
+        <v>196.065997</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>460.521069</v>
+        <v>517.365351</v>
       </c>
       <c r="D8" t="n">
-        <v>273.729863</v>
+        <v>308.086904</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>97.752433</v>
+        <v>109.818475</v>
       </c>
       <c r="D9" t="n">
-        <v>274.876494</v>
+        <v>309.377453</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>63.672923</v>
+        <v>71.532371</v>
       </c>
       <c r="D10" t="n">
-        <v>235.126559</v>
+        <v>264.638328</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>112.850827</v>
+        <v>126.780535</v>
       </c>
       <c r="D11" t="n">
-        <v>248.422737</v>
+        <v>279.603369</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>353.625303</v>
+        <v>397.274938</v>
       </c>
       <c r="D12" t="n">
-        <v>221.613234</v>
+        <v>249.428887</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>316.12939</v>
+        <v>355.150728</v>
       </c>
       <c r="D13" t="n">
-        <v>185.56085</v>
+        <v>208.85141</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>379.793049</v>
+        <v>426.672692</v>
       </c>
       <c r="D14" t="n">
-        <v>192.835729</v>
+        <v>217.03939</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>209.545244</v>
+        <v>235.410399</v>
       </c>
       <c r="D15" t="n">
-        <v>151.67965</v>
+        <v>170.717631</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>269.458931</v>
+        <v>302.719515</v>
       </c>
       <c r="D16" t="n">
-        <v>174.078874</v>
+        <v>195.92828</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>260.166931</v>
+        <v>292.28056</v>
       </c>
       <c r="D17" t="n">
-        <v>327.227575</v>
+        <v>368.299348</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>304.740742</v>
+        <v>342.356326</v>
       </c>
       <c r="D18" t="n">
-        <v>179.558663</v>
+        <v>202.095862</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>339.693164</v>
+        <v>381.623089</v>
       </c>
       <c r="D19" t="n">
-        <v>210.594249</v>
+        <v>237.026861</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>343.217773</v>
+        <v>385.582757</v>
       </c>
       <c r="D20" t="n">
-        <v>323.070538</v>
+        <v>363.620543</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>112.435538</v>
+        <v>126.313985</v>
       </c>
       <c r="D21" t="n">
-        <v>250.761777</v>
+        <v>282.235992</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>169.914181</v>
+        <v>190.887488</v>
       </c>
       <c r="D22" t="n">
-        <v>173.870114</v>
+        <v>195.693318</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>126.627774</v>
+        <v>142.258036</v>
       </c>
       <c r="D23" t="n">
-        <v>114.059732</v>
+        <v>128.375871</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>94.777973</v>
+        <v>106.476864</v>
       </c>
       <c r="D24" t="n">
-        <v>182.297456</v>
+        <v>205.178413</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>281.618259</v>
+        <v>316.379726</v>
       </c>
       <c r="D25" t="n">
-        <v>137.280958</v>
+        <v>154.511696</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>118.535727</v>
+        <v>133.167149</v>
       </c>
       <c r="D26" t="n">
-        <v>247.833204</v>
+        <v>278.939841</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>246.8091</v>
+        <v>277.273908</v>
       </c>
       <c r="D27" t="n">
-        <v>311.364437</v>
+        <v>350.445158</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>126.676129</v>
+        <v>142.31236</v>
       </c>
       <c r="D28" t="n">
-        <v>147.986687</v>
+        <v>166.561147</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>200.370526</v>
+        <v>225.103203</v>
       </c>
       <c r="D29" t="n">
-        <v>236.54198</v>
+        <v>266.231406</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>103.901819</v>
+        <v>116.726909</v>
       </c>
       <c r="D30" t="n">
-        <v>162.538764</v>
+        <v>182.93972</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>69.528921</v>
+        <v>78.111203</v>
       </c>
       <c r="D31" t="n">
-        <v>224.494731</v>
+        <v>252.672053</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>250.422569</v>
+        <v>281.333405</v>
       </c>
       <c r="D32" t="n">
-        <v>330.416897</v>
+        <v>371.888976</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>214.293243</v>
+        <v>240.744466</v>
       </c>
       <c r="D33" t="n">
-        <v>281.381671</v>
+        <v>316.699124</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>457.89642</v>
+        <v>514.41673</v>
       </c>
       <c r="D34" t="n">
-        <v>324.997647</v>
+        <v>365.789533</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>475.51964</v>
+        <v>534.215266</v>
       </c>
       <c r="D35" t="n">
-        <v>187.293147</v>
+        <v>210.801134</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>318.489473</v>
+        <v>357.802127</v>
       </c>
       <c r="D36" t="n">
-        <v>304.844062</v>
+        <v>343.106383</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>291.617045</v>
+        <v>327.612709</v>
       </c>
       <c r="D37" t="n">
-        <v>326.928036</v>
+        <v>367.962214</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>150.546353</v>
+        <v>169.128997</v>
       </c>
       <c r="D38" t="n">
-        <v>182.517799</v>
+        <v>205.426412</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>480.978899</v>
+        <v>540.348387</v>
       </c>
       <c r="D39" t="n">
-        <v>286.058427</v>
+        <v>321.96288</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>146.501636</v>
+        <v>164.585023</v>
       </c>
       <c r="D40" t="n">
-        <v>210.648996</v>
+        <v>237.088479</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>319.995391</v>
+        <v>359.493928</v>
       </c>
       <c r="D41" t="n">
-        <v>184.629201</v>
+        <v>207.802825</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>206.224442</v>
+        <v>231.679696</v>
       </c>
       <c r="D42" t="n">
-        <v>259.221968</v>
+        <v>291.758059</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>340.183243</v>
+        <v>382.173661</v>
       </c>
       <c r="D43" t="n">
-        <v>280.523583</v>
+        <v>315.733333</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>435.991891</v>
+        <v>489.808421</v>
       </c>
       <c r="D44" t="n">
-        <v>337.465616</v>
+        <v>379.822411</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
